--- a/data/trans_camb/P32A-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P32A-Provincia-trans_camb.xlsx
@@ -677,27 +677,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,87; 15,66</t>
+          <t>4,84; 16,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 6,2</t>
+          <t>-2,72; 6,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 1,23</t>
+          <t>-5,71; 1,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,09; 10,73</t>
+          <t>1,66; 12,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,88; 11,1</t>
+          <t>0,88; 10,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -707,17 +707,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,71; 11,37</t>
+          <t>3,51; 11,86</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 5,89</t>
+          <t>-0,7; 6,13</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 0,63</t>
+          <t>-3,86; 1,0</t>
         </is>
       </c>
     </row>
@@ -783,17 +783,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>52,74; 1055,72</t>
+          <t>62,93; 1350,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-61,58; 424,16</t>
+          <t>-60,71; 579,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 234,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>66,52; 1240,44</t>
+          <t>79,78; 1172,18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-31,55; 644,1</t>
+          <t>-29,02; 631,39</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 225,99</t>
         </is>
       </c>
     </row>
@@ -893,27 +893,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 1,68</t>
+          <t>-3,37; 1,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 2,82</t>
+          <t>-2,92; 2,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 0,27</t>
+          <t>-4,12; 0,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,98</t>
+          <t>0,0; 3,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,17</t>
+          <t>0,0; 6,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -923,17 +923,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 1,33</t>
+          <t>-2,51; 1,31</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 2,37</t>
+          <t>-1,91; 2,43</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 0,02</t>
+          <t>-3,19; 0,04</t>
         </is>
       </c>
     </row>
@@ -999,12 +999,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 289,37</t>
+          <t>-95,4; 453,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-74,55; 336,89</t>
+          <t>-75,41; 364,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-89,68; 229,68</t>
+          <t>-89,73; 229,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-71,07; 339,27</t>
+          <t>-75,16; 354,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1109,17 +1109,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 0,94</t>
+          <t>-1,67; 0,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 0,86</t>
+          <t>-1,67; 0,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,02; 6,33</t>
+          <t>1,14; 6,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1134,22 +1134,22 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,87</t>
+          <t>0,0; 4,08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 0,58</t>
+          <t>-1,51; 0,58</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 0,53</t>
+          <t>-1,51; 0,53</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,14; 5,01</t>
+          <t>1,02; 4,92</t>
         </is>
       </c>
     </row>
@@ -1325,42 +1325,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 2,09</t>
+          <t>-1,26; 2,43</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 1,61</t>
+          <t>-1,64; 1,36</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 2,99</t>
+          <t>-1,2; 2,83</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 0,0</t>
+          <t>-3,5; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 0,0</t>
+          <t>-3,53; 0,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 2,47</t>
+          <t>-1,41; 2,59</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 1,42</t>
+          <t>-1,28; 1,49</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 0,66</t>
+          <t>-1,54; 0,66</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-68,44; —</t>
+          <t>-62,3; —</t>
         </is>
       </c>
     </row>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 7,5</t>
+          <t>-0,36; 7,58</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 7,46</t>
+          <t>-0,91; 7,26</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 0,0</t>
+          <t>-4,73; 0,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,36</t>
+          <t>0,0; 9,59</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1566,22 +1566,22 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,67</t>
+          <t>0,0; 23,83</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,15; 5,76</t>
+          <t>0,4; 6,05</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 5,33</t>
+          <t>-0,5; 5,29</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 4,68</t>
+          <t>-1,25; 4,53</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 1,16</t>
+          <t>-3,21; 1,17</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 2,93</t>
+          <t>-2,19; 2,48</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 4,81</t>
+          <t>-0,76; 4,83</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,41</t>
+          <t>0,0; 5,31</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,14</t>
+          <t>0,0; 7,05</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,55; 6,04</t>
+          <t>0,57; 6,36</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 1,47</t>
+          <t>-1,36; 1,52</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 2,98</t>
+          <t>-0,76; 3,03</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,11; 4,24</t>
+          <t>0,11; 4,21</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 3,71</t>
+          <t>0,08; 4,01</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1,14; 5,6</t>
+          <t>1,37; 6,15</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 3,6</t>
+          <t>0,01; 3,77</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,35</t>
+          <t>0,0; 2,43</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,18</t>
+          <t>0,47; 4,24</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,25; 5,36</t>
+          <t>0,35; 5,19</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,14; 2,75</t>
+          <t>0,18; 2,69</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1,25; 4,26</t>
+          <t>1,25; 4,34</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,13; 3,49</t>
+          <t>0,01; 3,23</t>
         </is>
       </c>
     </row>
@@ -2079,17 +2079,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-55,33; —</t>
+          <t>-53,03; —</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>18,91; —</t>
+          <t>15,72; —</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-69,19; —</t>
+          <t>-62,58; —</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -2109,17 +2109,17 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-34,23; —</t>
+          <t>-30,34; —</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>45,05; —</t>
+          <t>67,03; —</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-7,56; —</t>
+          <t>-17,08; —</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 2,9</t>
+          <t>-0,21; 2,9</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 0,83</t>
+          <t>-0,84; 0,85</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 2,19</t>
+          <t>-0,47; 2,07</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 0,0</t>
+          <t>-2,99; 0,0</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 2,84</t>
+          <t>-1,29; 2,68</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 2,13</t>
+          <t>-1,71; 2,14</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 1,7</t>
+          <t>-0,51; 1,56</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 1,03</t>
+          <t>-0,57; 1,1</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 1,53</t>
+          <t>-0,52; 1,49</t>
         </is>
       </c>
     </row>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-54,92; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2325,17 +2325,17 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-68,56; 657,47</t>
+          <t>-69,26; 696,51</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-69,24; 387,4</t>
+          <t>-75,32; 368,13</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-74,88; 673,08</t>
+          <t>-75,36; 621,58</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,44</t>
+          <t>0,7; 2,44</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>0,08; 1,79</t>
+          <t>0,22; 1,83</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 1,5</t>
+          <t>0,02; 1,57</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 1,32</t>
+          <t>-0,12; 1,34</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,91</t>
+          <t>0,35; 1,85</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,12; 2,15</t>
+          <t>0,09; 2,02</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,53; 1,85</t>
+          <t>0,54; 1,78</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,48</t>
+          <t>0,37; 1,55</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,45</t>
+          <t>0,15; 1,41</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>35,22; 313,78</t>
+          <t>45,47; 329,99</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>2,89; 243,6</t>
+          <t>12,23; 231,6</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 209,32</t>
+          <t>-5,71; 205,86</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-55,61; 1060,29</t>
+          <t>-61,07; 1054,78</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 1561,1</t>
+          <t>19,66; 1672,48</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 1608,61</t>
+          <t>-6,28; 1461,11</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>45,1; 301,28</t>
+          <t>44,22; 296,91</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>34,53; 244,29</t>
+          <t>35,33; 257,56</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>13,35; 244,66</t>
+          <t>12,4; 232,86</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P32A-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P32A-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-2,01</t>
+          <t>-2,15</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-1,34</t>
+          <t>-1,47</t>
         </is>
       </c>
     </row>
@@ -677,27 +677,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,84; 16,1</t>
+          <t>4,19; 15,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 6,58</t>
+          <t>-2,64; 6,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,71; 1,05</t>
+          <t>-5,56; 0,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,66; 12,47</t>
+          <t>1,11; 10,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,88; 10,32</t>
+          <t>0,88; 10,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -707,17 +707,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,51; 11,86</t>
+          <t>4,0; 12,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 6,13</t>
+          <t>-0,77; 5,93</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 1,0</t>
+          <t>-4,19; 0,31</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-61,02%</t>
+          <t>-65,15%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-61,06%</t>
+          <t>-66,69%</t>
         </is>
       </c>
     </row>
@@ -783,17 +783,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>62,93; 1350,81</t>
+          <t>56,6; 1100,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-60,71; 579,43</t>
+          <t>-58,77; 496,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 127,77</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>79,78; 1172,18</t>
+          <t>72,98; 1182,3</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-29,02; 631,39</t>
+          <t>-38,2; 582,21</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 225,99</t>
+          <t>-100,0; 134,26</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-1,76</t>
+          <t>-1,75</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-1,37</t>
+          <t>-1,36</t>
         </is>
       </c>
     </row>
@@ -893,27 +893,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 1,8</t>
+          <t>-3,5; 1,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 2,77</t>
+          <t>-2,81; 2,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 0,15</t>
+          <t>-4,39; 0,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,51</t>
+          <t>0,0; 3,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,37</t>
+          <t>0,0; 4,41</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -923,17 +923,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 1,31</t>
+          <t>-2,59; 1,35</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 2,43</t>
+          <t>-1,76; 2,55</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 0,04</t>
+          <t>-3,32; 0,05</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-76,99%</t>
+          <t>-76,22%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-78,89%</t>
+          <t>-78,47%</t>
         </is>
       </c>
     </row>
@@ -999,12 +999,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-95,4; 453,63</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-75,41; 364,02</t>
+          <t>-79,25; 351,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-89,73; 229,62</t>
+          <t>-87,4; 325,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-75,16; 354,68</t>
+          <t>-70,06; 376,35</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3,45</t>
+          <t>3,71</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,16</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2,69</t>
+          <t>2,89</t>
         </is>
       </c>
     </row>
@@ -1109,17 +1109,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 0,94</t>
+          <t>-1,66; 0,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 0,85</t>
+          <t>-1,72; 0,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,14; 6,78</t>
+          <t>1,07; 6,6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,08</t>
+          <t>0,0; 3,91</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,02; 4,92</t>
+          <t>1,19; 5,15</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>634,84%</t>
+          <t>682,88%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>714,3%</t>
+          <t>768,08%</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,58</t>
+          <t>0,38</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,68</t>
+          <t>0,63</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,62</t>
+          <t>0,47</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 2,43</t>
+          <t>-1,54; 2,24</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 1,36</t>
+          <t>-1,66; 1,64</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 2,83</t>
+          <t>-1,25; 2,32</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 0,0</t>
+          <t>-4,07; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 0,0</t>
+          <t>-4,61; 0,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 2,59</t>
+          <t>-1,55; 2,18</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 1,49</t>
+          <t>-1,26; 1,22</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 0,66</t>
+          <t>-1,61; 0,66</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 2,11</t>
+          <t>-0,89; 1,76</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>70,83%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>60,73%</t>
         </is>
       </c>
     </row>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-62,3; —</t>
+          <t>-74,62; 851,36</t>
         </is>
       </c>
     </row>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,13</t>
+          <t>4,33</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,49</t>
+          <t>0,42</t>
         </is>
       </c>
     </row>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 7,58</t>
+          <t>-0,21; 7,64</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 7,26</t>
+          <t>-0,83; 7,42</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 0,0</t>
+          <t>-4,84; 0,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,59</t>
+          <t>0,0; 8,37</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1566,22 +1566,22 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,83</t>
+          <t>0,0; 23,6</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,4; 6,05</t>
+          <t>0,28; 6,17</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 5,29</t>
+          <t>-0,51; 5,32</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 4,53</t>
+          <t>-1,24; 4,22</t>
         </is>
       </c>
     </row>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>78,37%</t>
+          <t>68,08%</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2,12</t>
+          <t>2,01</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,3</t>
+          <t>2,27</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2,18</t>
+          <t>2,1</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 1,17</t>
+          <t>-3,51; 1,16</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 2,48</t>
+          <t>-2,19; 2,5</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 4,83</t>
+          <t>-0,88; 4,75</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,31</t>
+          <t>0,0; 5,63</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,05</t>
+          <t>0,0; 7,38</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,57; 6,36</t>
+          <t>0,56; 6,33</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 1,52</t>
+          <t>-1,52; 1,51</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 3,03</t>
+          <t>-0,73; 2,89</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,11; 4,21</t>
+          <t>0,03; 4,08</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>237,97%</t>
+          <t>225,67%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>384,15%</t>
+          <t>369,46%</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1,57</t>
+          <t>1,92</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,99</t>
+          <t>5,53</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1,65</t>
+          <t>3,31</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,08; 4,01</t>
+          <t>-0,0; 3,88</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1,37; 6,15</t>
+          <t>1,33; 6,15</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,01; 3,77</t>
+          <t>0,09; 4,3</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,43</t>
+          <t>0,0; 2,72</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,24</t>
+          <t>0,44; 4,12</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,35; 5,19</t>
+          <t>2,86; 10,17</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,18; 2,69</t>
+          <t>0,09; 2,66</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1,25; 4,34</t>
+          <t>1,11; 4,15</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,01; 3,23</t>
+          <t>1,73; 5,48</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>248,2%</t>
+          <t>303,6%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>379,69%</t>
+          <t>762,27%</t>
         </is>
       </c>
     </row>
@@ -2079,17 +2079,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-53,03; —</t>
+          <t>-48,21; —</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>15,72; —</t>
+          <t>23,09; —</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-62,58; —</t>
+          <t>-64,8; —</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -2109,17 +2109,17 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-30,34; —</t>
+          <t>-51,98; —</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>67,03; —</t>
+          <t>58,83; —</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-17,08; —</t>
+          <t>52,33; —</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>0,46</t>
+          <t>0,45</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,28</t>
+          <t>0,27</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 2,9</t>
+          <t>-0,2; 2,92</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 0,85</t>
+          <t>-0,85; 0,81</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 2,07</t>
+          <t>-0,5; 2,12</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 0,0</t>
+          <t>-3,14; 0,0</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 2,68</t>
+          <t>-1,3; 2,84</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 2,14</t>
+          <t>-1,7; 2,06</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 1,56</t>
+          <t>-0,51; 1,58</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 1,1</t>
+          <t>-0,56; 1,15</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 1,49</t>
+          <t>-0,58; 1,51</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>86,92%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-16,86%</t>
+          <t>-16,94%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>43,24%</t>
         </is>
       </c>
     </row>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-66,73; —</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2325,17 +2325,17 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-69,26; 696,51</t>
+          <t>-70,46; 679,98</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-75,32; 368,13</t>
+          <t>-67,1; 456,37</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-75,36; 621,58</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>0,71</t>
+          <t>0,75</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,05</t>
+          <t>1,83</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>0,79</t>
+          <t>1,11</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,44</t>
+          <t>0,67; 2,47</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,83</t>
+          <t>0,13; 1,71</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>0,02; 1,57</t>
+          <t>0,03; 1,52</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 1,34</t>
+          <t>-0,12; 1,33</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,85</t>
+          <t>0,28; 1,93</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,09; 2,02</t>
+          <t>0,87; 3,14</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,54; 1,78</t>
+          <t>0,52; 1,77</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,55</t>
+          <t>0,37; 1,51</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,41</t>
+          <t>0,51; 1,77</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>66,54%</t>
+          <t>70,3%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>317,94%</t>
+          <t>551,71%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>133,22%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>45,47; 329,99</t>
+          <t>37,81; 318,16</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>12,23; 231,6</t>
+          <t>6,24; 232,6</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-5,71; 205,86</t>
+          <t>-0,85; 199,79</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-61,07; 1054,78</t>
+          <t>-45,93; 1299,42</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>19,66; 1672,48</t>
+          <t>0,08; 1448,3</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 1461,11</t>
+          <t>98,61; 2466,16</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>44,22; 296,91</t>
+          <t>42,03; 280,97</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>35,33; 257,56</t>
+          <t>29,33; 239,18</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>12,4; 232,86</t>
+          <t>43,54; 301,36</t>
         </is>
       </c>
     </row>
